--- a/data/trans_dic/P1409-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1409-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,8</t>
+          <t>1,66; 3,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,49</t>
+          <t>2,07; 4,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 7,31</t>
+          <t>3,38; 6,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,27</t>
+          <t>2,23; 4,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,11</t>
+          <t>3,24; 6,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,97; 7,62</t>
+          <t>4,83; 7,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,68</t>
+          <t>2,27; 3,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,0</t>
+          <t>2,99; 4,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 6,99</t>
+          <t>4,68; 6,69</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,32</t>
+          <t>1,16; 2,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,31</t>
+          <t>1,93; 3,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,63</t>
+          <t>2,63; 4,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,12</t>
+          <t>1,71; 3,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 4,79</t>
+          <t>3,07; 4,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 16,91</t>
+          <t>3,58; 5,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,46</t>
+          <t>1,56; 2,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 3,78</t>
+          <t>2,67; 3,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,38; 11,01</t>
+          <t>3,37; 4,66</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,41</t>
+          <t>0,6; 3,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,33</t>
+          <t>0,85; 3,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,55</t>
+          <t>2,54; 6,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,61</t>
+          <t>1,4; 4,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,58</t>
+          <t>2,4; 5,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,18</t>
+          <t>3,34; 5,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,47</t>
+          <t>1,42; 3,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,91</t>
+          <t>1,81; 3,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 4,98</t>
+          <t>3,32; 5,68</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,43</t>
+          <t>1,49; 2,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,16</t>
+          <t>2,04; 3,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 4,65</t>
+          <t>3,15; 4,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,31</t>
+          <t>2,2; 3,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 4,68</t>
+          <t>3,35; 4,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 12,52</t>
+          <t>4,2; 5,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 2,69</t>
+          <t>1,99; 2,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 3,72</t>
+          <t>2,87; 3,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 8,9</t>
+          <t>3,88; 4,9</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26897</t>
+          <t>27762</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46765</t>
+          <t>49714</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>73662</t>
+          <t>77476</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16753; 37028</t>
+          <t>16166; 36355</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15708; 33861</t>
+          <t>15627; 33851</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18106; 37484</t>
+          <t>19500; 38718</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30928; 57133</t>
+          <t>29753; 57617</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30359; 60749</t>
+          <t>32196; 60276</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37362; 57233</t>
+          <t>39597; 60648</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52647; 85064</t>
+          <t>52550; 87139</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>52664; 87457</t>
+          <t>52344; 86120</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62063; 88300</t>
+          <t>65385; 93323</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76587</t>
+          <t>78652</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>156417</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>233005</t>
+          <t>173800</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22693; 45563</t>
+          <t>22872; 45175</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39619; 68689</t>
+          <t>40141; 69996</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51065; 106029</t>
+          <t>58648; 104534</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29120; 54827</t>
+          <t>29925; 55350</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59640; 95281</t>
+          <t>61071; 94565</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>80719; 378212</t>
+          <t>77576; 113032</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56940; 91444</t>
+          <t>57905; 92286</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>106705; 153820</t>
+          <t>108528; 154621</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>152782; 498205</t>
+          <t>148266; 204992</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23215</t>
+          <t>28880</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26165</t>
+          <t>32835</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49380</t>
+          <t>61715</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2926; 16428</t>
+          <t>2889; 16707</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4179; 18218</t>
+          <t>4643; 18883</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14781; 35911</t>
+          <t>18041; 43784</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6900; 21142</t>
+          <t>6437; 20835</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12837; 30619</t>
+          <t>13174; 30808</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18826; 34154</t>
+          <t>24528; 43760</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12342; 32639</t>
+          <t>13302; 32893</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19835; 42840</t>
+          <t>19869; 42297</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37249; 65094</t>
+          <t>47937; 82023</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>126700</t>
+          <t>135294</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>229348</t>
+          <t>177696</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>356047</t>
+          <t>312990</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>50948; 83159</t>
+          <t>50997; 82718</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>68290; 106886</t>
+          <t>68738; 105133</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>97110; 160294</t>
+          <t>110697; 166222</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>77103; 117618</t>
+          <t>78193; 116828</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>117587; 165283</t>
+          <t>118293; 167710</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>153227; 456730</t>
+          <t>156502; 200575</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>137717; 187542</t>
+          <t>138651; 188861</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>198888; 257075</t>
+          <t>198522; 256899</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>269990; 631558</t>
+          <t>280931; 354577</t>
         </is>
       </c>
     </row>
